--- a/config/yunying/double11_lottery.xlsx
+++ b/config/yunying/double11_lottery.xlsx
@@ -1220,7 +1220,7 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>1等賞</t>
+          <t>一等奖</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>2等賞</t>
+          <t>二等奖</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>3等賞</t>
+          <t>三等奖</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>ラッキー賞</t>
+          <t>幸运奖</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>1等賞</t>
+          <t>一等奖</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>2等賞</t>
+          <t>二等奖</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>3等賞</t>
+          <t>三等奖</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>ラッキー賞</t>
+          <t>幸运奖</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
